--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,158 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
+        <v>100</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="V8" s="3">
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -848,16 +861,16 @@
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
@@ -865,50 +878,56 @@
       <c r="U9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
@@ -919,13 +938,19 @@
         <v>100</v>
       </c>
       <c r="T10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="V10" s="3">
+        <v>100</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,67 +972,75 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>800</v>
-      </c>
-      <c r="G12" s="3">
-        <v>400</v>
       </c>
       <c r="H12" s="3">
         <v>800</v>
       </c>
       <c r="I12" s="3">
+        <v>400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>800</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>500</v>
-      </c>
-      <c r="K12" s="3">
-        <v>400</v>
       </c>
       <c r="L12" s="3">
         <v>500</v>
       </c>
       <c r="M12" s="3">
+        <v>400</v>
+      </c>
+      <c r="N12" s="3">
+        <v>500</v>
+      </c>
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
-        <v>100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
       <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
-        <v>100</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
+        <v>100</v>
+      </c>
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,8 +1098,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1094,11 +1133,11 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1124,8 +1163,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,11 +1198,11 @@
       <c r="K15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1169,13 +1214,13 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1183,8 +1228,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1254,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2800</v>
       </c>
       <c r="M17" s="3">
         <v>1300</v>
       </c>
       <c r="N17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1200</v>
       </c>
       <c r="U17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2400</v>
       </c>
       <c r="I18" s="3">
         <v>-1500</v>
       </c>
       <c r="J18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1409,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1403,67 +1470,79 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-1200</v>
       </c>
       <c r="U21" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,67 +1600,79 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1639,8 +1730,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1795,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1200</v>
       </c>
       <c r="U27" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1990,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1889,11 +2010,11 @@
       <c r="F29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -1908,34 +2029,40 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>1500</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>100</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>100</v>
+      </c>
+      <c r="T29" s="3">
+        <v>100</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2120,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2185,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2111,67 +2250,79 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1200</v>
       </c>
       <c r="U33" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2380,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1200</v>
       </c>
       <c r="U35" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2544,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,75 +2569,83 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>3200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>300</v>
@@ -2478,26 +2657,26 @@
         <v>300</v>
       </c>
       <c r="I42" s="3">
+        <v>300</v>
+      </c>
+      <c r="J42" s="3">
+        <v>300</v>
+      </c>
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2508,57 +2687,63 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>100</v>
+      </c>
+      <c r="W42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
-        <v>100</v>
-      </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
@@ -2567,21 +2752,27 @@
         <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>200</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
+        <v>300</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
@@ -2605,10 +2796,10 @@
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
@@ -2629,58 +2820,64 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
+        <v>100</v>
+      </c>
+      <c r="U44" s="3">
+        <v>100</v>
+      </c>
+      <c r="V44" s="3">
         <v>200</v>
       </c>
-      <c r="U44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>400</v>
+      </c>
+      <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
-      </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
@@ -2693,106 +2890,118 @@
       <c r="U45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>0</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>10</v>
+      <c r="L47" s="3">
+        <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O47" s="3">
         <v>400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
@@ -2805,28 +3014,34 @@
       <c r="S47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
@@ -2835,10 +3050,10 @@
         <v>400</v>
       </c>
       <c r="J48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
@@ -2847,31 +3062,37 @@
         <v>500</v>
       </c>
       <c r="N48" s="3">
+        <v>500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>500</v>
+      </c>
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>600</v>
       </c>
       <c r="T48" s="3">
         <v>600</v>
       </c>
       <c r="U48" s="3">
+        <v>600</v>
+      </c>
+      <c r="V48" s="3">
+        <v>600</v>
+      </c>
+      <c r="W48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2888,10 +3109,10 @@
         <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J49" s="3">
         <v>400</v>
@@ -2903,10 +3124,10 @@
         <v>400</v>
       </c>
       <c r="M49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
@@ -2924,13 +3145,19 @@
         <v>300</v>
       </c>
       <c r="T49" s="3">
+        <v>300</v>
+      </c>
+      <c r="U49" s="3">
+        <v>300</v>
+      </c>
+      <c r="V49" s="3">
         <v>200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3215,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3280,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3106,8 +3345,14 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3410,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F54" s="3">
         <v>5200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>13300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3504,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,31 +3529,33 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3306,31 +3567,37 @@
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3343,11 +3610,11 @@
       <c r="F58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -3364,11 +3631,11 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>10</v>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>10</v>
@@ -3382,22 +3649,28 @@
       <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -3418,54 +3691,60 @@
         <v>100</v>
       </c>
       <c r="L59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>300</v>
       </c>
       <c r="G60" s="3">
         <v>200</v>
       </c>
       <c r="H60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I60" s="3">
         <v>200</v>
@@ -3480,34 +3759,40 @@
         <v>200</v>
       </c>
       <c r="M60" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N60" s="3">
         <v>200</v>
       </c>
       <c r="O60" s="3">
+        <v>400</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
-        <v>100</v>
-      </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
       </c>
       <c r="S60" s="3">
+        <v>100</v>
+      </c>
+      <c r="T60" s="3">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
-        <v>100</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,8 +3850,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,10 +3865,10 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
@@ -3595,10 +3886,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -3606,11 +3897,11 @@
       <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>10</v>
+      <c r="P62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>100</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>10</v>
@@ -3624,8 +3915,14 @@
       <c r="U62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3980,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +4045,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,20 +4110,26 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3">
         <v>800</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
       </c>
@@ -3824,44 +4139,50 @@
       <c r="I66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J66" s="3">
-        <v>100</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
+      <c r="J66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L66" s="3">
+        <v>100</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>300</v>
       </c>
-      <c r="P66" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>100</v>
-      </c>
       <c r="R66" s="3">
+        <v>100</v>
+      </c>
+      <c r="S66" s="3">
+        <v>100</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4204,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4265,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4330,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4395,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4460,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-44500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-42200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-40900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-39100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-37600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-35200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-33800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-31800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-30700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-28100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-28500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-27800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-25700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-24800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-23900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-22800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4590,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4655,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4720,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4850,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1200</v>
       </c>
       <c r="U81" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +5014,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4664,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4678,8 +5075,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +5140,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5205,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5270,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5335,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5400,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-1200</v>
       </c>
       <c r="G89" s="3">
         <v>-1200</v>
       </c>
       <c r="H89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
       </c>
       <c r="L89" s="3">
         <v>-1200</v>
       </c>
       <c r="M89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5494,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5064,31 +5505,31 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>10</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>10</v>
@@ -5099,8 +5540,8 @@
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>10</v>
@@ -5108,14 +5549,20 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5620,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5685,14 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5241,22 +5700,22 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5265,14 +5724,14 @@
         <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -5286,13 +5745,19 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5779,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5840,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5905,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5970,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,20 +6035,26 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -5577,63 +6068,69 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>4000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>9400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5668,63 +6165,75 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-1200</v>
       </c>
       <c r="H102" s="3">
         <v>-1300</v>
       </c>
       <c r="I102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
-        <v>-1200</v>
-      </c>
       <c r="K102" s="3">
-        <v>2800</v>
+        <v>-1300</v>
       </c>
       <c r="L102" s="3">
         <v>-1200</v>
       </c>
       <c r="M102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O102" s="3">
         <v>8800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,123 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
@@ -781,7 +785,7 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -790,42 +794,45 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -855,25 +862,25 @@
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
@@ -884,25 +891,28 @@
       <c r="W9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>200</v>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -911,7 +921,7 @@
         <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -920,37 +930,40 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
       </c>
       <c r="Q12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
-        <v>100</v>
-      </c>
       <c r="U12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>200</v>
       </c>
       <c r="W12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="X12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1139,8 +1159,8 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1204,8 +1227,8 @@
       <c r="M15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1220,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,64 +1282,65 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1200</v>
       </c>
       <c r="V17" s="3">
         <v>1200</v>
@@ -1321,73 +1348,79 @@
       <c r="W17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-1100</v>
       </c>
       <c r="V18" s="3">
         <v>-1100</v>
       </c>
       <c r="W18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1476,73 +1510,79 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,73 +1646,79 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-1200</v>
       </c>
       <c r="W23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-1200</v>
       </c>
       <c r="W26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2016,8 +2077,8 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2035,11 +2096,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>1500</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -2047,13 +2108,13 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
         <v>100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
+      <c r="U29" s="3">
+        <v>100</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2256,73 +2326,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1300</v>
       </c>
       <c r="U41" s="3">
         <v>1300</v>
       </c>
       <c r="V41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2648,7 +2738,7 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>300</v>
@@ -2663,23 +2753,23 @@
         <v>300</v>
       </c>
       <c r="K42" s="3">
+        <v>300</v>
+      </c>
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2693,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
         <v>100</v>
@@ -2701,81 +2791,87 @@
       <c r="W42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>500</v>
       </c>
       <c r="M43" s="3">
+        <v>500</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
-      </c>
-      <c r="T43" s="3">
-        <v>300</v>
       </c>
       <c r="U43" s="3">
         <v>300</v>
       </c>
       <c r="V43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
@@ -2802,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
@@ -2826,61 +2922,64 @@
         <v>100</v>
       </c>
       <c r="V44" s="3">
+        <v>100</v>
+      </c>
+      <c r="W44" s="3">
         <v>200</v>
       </c>
-      <c r="W44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>300</v>
       </c>
       <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
@@ -2896,81 +2995,87 @@
       <c r="W45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>0</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>10</v>
+      <c r="E47" s="3">
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>10</v>
@@ -2987,8 +3092,8 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2996,15 +3101,15 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="3">
         <v>400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3020,14 +3125,17 @@
       <c r="U47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3038,13 +3146,13 @@
         <v>400</v>
       </c>
       <c r="F48" s="3">
+        <v>400</v>
+      </c>
+      <c r="G48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>400</v>
       </c>
       <c r="I48" s="3">
         <v>400</v>
@@ -3056,7 +3164,7 @@
         <v>400</v>
       </c>
       <c r="L48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M48" s="3">
         <v>500</v>
@@ -3068,19 +3176,19 @@
         <v>500</v>
       </c>
       <c r="P48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q48" s="3">
         <v>600</v>
       </c>
       <c r="R48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="S48" s="3">
         <v>500</v>
       </c>
       <c r="T48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>600</v>
@@ -3089,10 +3197,13 @@
         <v>600</v>
       </c>
       <c r="W48" s="3">
+        <v>600</v>
+      </c>
+      <c r="X48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3115,7 +3226,7 @@
         <v>500</v>
       </c>
       <c r="J49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K49" s="3">
         <v>400</v>
@@ -3130,7 +3241,7 @@
         <v>400</v>
       </c>
       <c r="O49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
@@ -3151,13 +3262,16 @@
         <v>300</v>
       </c>
       <c r="V49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2000</v>
-      </c>
-      <c r="T54" s="3">
-        <v>2700</v>
       </c>
       <c r="U54" s="3">
         <v>2700</v>
       </c>
       <c r="V54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W54" s="3">
         <v>3500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,28 +3661,29 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
@@ -3561,19 +3692,19 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
-        <v>100</v>
-      </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
-        <v>100</v>
-      </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3582,22 +3713,25 @@
         <v>0</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3616,8 +3750,8 @@
       <c r="H58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3637,8 +3771,8 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>10</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>10</v>
@@ -3655,14 +3789,17 @@
       <c r="U58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3673,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
@@ -3697,19 +3834,19 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
         <v>300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -3718,16 +3855,19 @@
         <v>0</v>
       </c>
       <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3735,19 +3875,19 @@
         <v>100</v>
       </c>
       <c r="E60" s="3">
+        <v>100</v>
+      </c>
+      <c r="F60" s="3">
         <v>300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>200</v>
       </c>
       <c r="J60" s="3">
         <v>200</v>
@@ -3765,16 +3905,16 @@
         <v>200</v>
       </c>
       <c r="O60" s="3">
+        <v>200</v>
+      </c>
+      <c r="P60" s="3">
         <v>400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>200</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -3783,16 +3923,19 @@
         <v>100</v>
       </c>
       <c r="U60" s="3">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
-        <v>100</v>
-      </c>
       <c r="W60" s="3">
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3871,7 +4017,7 @@
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -3892,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -3903,8 +4049,8 @@
       <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>10</v>
+      <c r="R62" s="3">
+        <v>100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>10</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,23 +4271,26 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="3">
-        <v>0</v>
+      <c r="E66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4145,44 +4303,47 @@
       <c r="K66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L66" s="3">
-        <v>100</v>
+      <c r="L66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>400</v>
-      </c>
-      <c r="P66" s="3">
-        <v>300</v>
       </c>
       <c r="Q66" s="3">
         <v>300</v>
       </c>
       <c r="R66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
       </c>
       <c r="T66" s="3">
+        <v>100</v>
+      </c>
+      <c r="U66" s="3">
         <v>200</v>
-      </c>
-      <c r="U66" s="3">
-        <v>300</v>
       </c>
       <c r="V66" s="3">
         <v>300</v>
       </c>
       <c r="W66" s="3">
+        <v>300</v>
+      </c>
+      <c r="X66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-46900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-40900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-37600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-35200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-25700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-24800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-23900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-22800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5025,10 +5224,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -5067,10 +5266,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,22 +5620,25 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1200</v>
       </c>
       <c r="H89" s="3">
         <v>-1200</v>
@@ -5430,13 +5647,13 @@
         <v>-1200</v>
       </c>
       <c r="J89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="K89" s="3">
         <v>-1300</v>
       </c>
       <c r="L89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="M89" s="3">
         <v>-1200</v>
@@ -5445,34 +5662,37 @@
         <v>-1200</v>
       </c>
       <c r="O89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-600</v>
       </c>
       <c r="R89" s="3">
         <v>-600</v>
       </c>
       <c r="S89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-700</v>
       </c>
       <c r="U89" s="3">
         <v>-700</v>
       </c>
       <c r="V89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,20 +5716,21 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -5517,22 +5738,22 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>10</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>10</v>
@@ -5546,23 +5767,26 @@
       <c r="R91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,20 +5918,23 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -5712,29 +5942,29 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -5751,13 +5981,16 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,23 +6284,26 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -6074,48 +6320,51 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>4000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>9400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>10</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>10</v>
@@ -6132,8 +6381,8 @@
       <c r="J101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-1300</v>
       </c>
       <c r="H102" s="3">
         <v>-1300</v>
       </c>
       <c r="I102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1300</v>
       </c>
       <c r="K102" s="3">
         <v>-1300</v>
       </c>
       <c r="L102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,19 +771,19 @@
         <v>100</v>
       </c>
       <c r="E8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
@@ -788,7 +792,7 @@
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -797,45 +801,48 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
       </c>
       <c r="Q8" s="3">
+        <v>200</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
-        <v>100</v>
-      </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -865,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
@@ -894,28 +901,31 @@
       <c r="X9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="3">
-        <v>200</v>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -924,7 +934,7 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -933,37 +943,40 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
       </c>
       <c r="Q12" s="3">
         <v>200</v>
       </c>
       <c r="R12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3">
-        <v>100</v>
-      </c>
       <c r="V12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W12" s="3">
         <v>200</v>
       </c>
       <c r="X12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,31 +1141,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1162,8 +1182,8 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1230,8 +1253,8 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1246,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="T15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,67 +1309,68 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1200</v>
       </c>
       <c r="W17" s="3">
         <v>1200</v>
@@ -1351,76 +1378,82 @@
       <c r="X17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1100</v>
       </c>
       <c r="W18" s="3">
         <v>-1100</v>
       </c>
       <c r="X18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1513,76 +1547,82 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,76 +1689,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-1200</v>
       </c>
       <c r="X23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-1200</v>
       </c>
       <c r="X26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,28 +2115,31 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2099,11 +2160,11 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>1500</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -2111,13 +2172,13 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
         <v>100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
+      <c r="V29" s="3">
+        <v>100</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2329,76 +2399,82 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,81 +2744,85 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>700</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1300</v>
       </c>
       <c r="V41" s="3">
         <v>1300</v>
       </c>
       <c r="W41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -2741,7 +2831,7 @@
         <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>300</v>
@@ -2756,23 +2846,23 @@
         <v>300</v>
       </c>
       <c r="L42" s="3">
+        <v>300</v>
+      </c>
+      <c r="M42" s="3">
         <v>600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2786,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>100</v>
@@ -2794,76 +2884,82 @@
       <c r="X42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>500</v>
       </c>
       <c r="N43" s="3">
+        <v>500</v>
+      </c>
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
-      </c>
-      <c r="U43" s="3">
-        <v>300</v>
       </c>
       <c r="V43" s="3">
         <v>300</v>
       </c>
       <c r="W43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2873,8 +2969,8 @@
       <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
@@ -2901,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -2925,64 +3021,67 @@
         <v>100</v>
       </c>
       <c r="W44" s="3">
+        <v>100</v>
+      </c>
+      <c r="X44" s="3">
         <v>200</v>
       </c>
-      <c r="X44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
       </c>
       <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
-        <v>100</v>
-      </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
@@ -2998,87 +3097,93 @@
       <c r="X45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3095,8 +3200,8 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3104,15 +3209,15 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="3">
         <v>400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3128,14 +3233,17 @@
       <c r="V47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3149,13 +3257,13 @@
         <v>400</v>
       </c>
       <c r="G48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>400</v>
@@ -3167,7 +3275,7 @@
         <v>400</v>
       </c>
       <c r="M48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>500</v>
@@ -3179,19 +3287,19 @@
         <v>500</v>
       </c>
       <c r="Q48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R48" s="3">
         <v>600</v>
       </c>
       <c r="S48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="T48" s="3">
         <v>500</v>
       </c>
       <c r="U48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="V48" s="3">
         <v>600</v>
@@ -3200,10 +3308,13 @@
         <v>600</v>
       </c>
       <c r="X48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3229,7 +3340,7 @@
         <v>500</v>
       </c>
       <c r="K49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L49" s="3">
         <v>400</v>
@@ -3244,7 +3355,7 @@
         <v>400</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
@@ -3265,13 +3376,16 @@
         <v>300</v>
       </c>
       <c r="W49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2000</v>
-      </c>
-      <c r="U54" s="3">
-        <v>2700</v>
       </c>
       <c r="V54" s="3">
         <v>2700</v>
       </c>
       <c r="W54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X54" s="3">
         <v>3500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,31 +3792,32 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -3695,19 +3826,19 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
-        <v>100</v>
-      </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3716,42 +3847,45 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>10</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3774,8 +3908,8 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>10</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>10</v>
@@ -3792,14 +3926,17 @@
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3813,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -3837,19 +3974,19 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -3858,39 +3995,42 @@
         <v>0</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
       <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
       </c>
       <c r="F60" s="3">
+        <v>100</v>
+      </c>
+      <c r="G60" s="3">
         <v>300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
@@ -3908,16 +4048,16 @@
         <v>200</v>
       </c>
       <c r="P60" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q60" s="3">
         <v>400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>200</v>
       </c>
       <c r="R60" s="3">
         <v>200</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -3926,16 +4066,19 @@
         <v>100</v>
       </c>
       <c r="V60" s="3">
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
-        <v>100</v>
-      </c>
       <c r="X60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4020,7 +4166,7 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4041,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -4052,8 +4198,8 @@
       <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>10</v>
+      <c r="S62" s="3">
+        <v>100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>10</v>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,8 +4429,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4285,15 +4443,15 @@
       <c r="E66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="3">
-        <v>0</v>
+      <c r="F66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4306,44 +4464,47 @@
       <c r="L66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M66" s="3">
-        <v>100</v>
+      <c r="M66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>300</v>
       </c>
       <c r="R66" s="3">
         <v>300</v>
       </c>
       <c r="S66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
       </c>
       <c r="U66" s="3">
+        <v>100</v>
+      </c>
+      <c r="V66" s="3">
         <v>200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>300</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-47600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-46900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-40900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-37600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-35200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-25700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-24800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-23900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-22800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5227,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -5269,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,25 +5837,28 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-1200</v>
       </c>
       <c r="I89" s="3">
         <v>-1200</v>
@@ -5650,13 +5867,13 @@
         <v>-1200</v>
       </c>
       <c r="K89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="L89" s="3">
         <v>-1300</v>
       </c>
       <c r="M89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="N89" s="3">
         <v>-1200</v>
@@ -5665,34 +5882,37 @@
         <v>-1200</v>
       </c>
       <c r="P89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-600</v>
       </c>
       <c r="S89" s="3">
         <v>-600</v>
       </c>
       <c r="T89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-700</v>
       </c>
       <c r="V89" s="3">
         <v>-700</v>
       </c>
       <c r="W89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,23 +5937,24 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -5741,22 +5962,22 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>10</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
@@ -5770,23 +5991,26 @@
       <c r="S91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,23 +6148,26 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -5945,29 +6175,29 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -5984,13 +6214,16 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,26 +6530,29 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -6323,40 +6569,43 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>4000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>9400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6366,8 +6615,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -6384,8 +6633,8 @@
       <c r="K101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-1300</v>
       </c>
       <c r="I102" s="3">
         <v>-1300</v>
       </c>
       <c r="J102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1300</v>
       </c>
       <c r="L102" s="3">
         <v>-1300</v>
       </c>
       <c r="M102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,137 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E7" s="2">
         <v>45443</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44804</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44712</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44620</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44074</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43982</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43890</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43799</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43708</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43616</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>100</v>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>200</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
@@ -795,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -804,48 +808,51 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
       </c>
       <c r="R8" s="3">
+        <v>200</v>
+      </c>
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -875,25 +882,25 @@
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
@@ -904,31 +911,34 @@
       <c r="Y9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -937,7 +947,7 @@
         <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
@@ -946,37 +956,40 @@
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3">
         <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
-        <v>3700</v>
-      </c>
       <c r="H12" s="3">
+        <v>500</v>
+      </c>
+      <c r="I12" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>200</v>
       </c>
       <c r="R12" s="3">
         <v>200</v>
       </c>
       <c r="S12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
-        <v>100</v>
-      </c>
       <c r="W12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X12" s="3">
         <v>200</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1159,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1170,8 +1190,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -1185,8 +1205,8 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1215,31 +1235,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>10</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>10</v>
@@ -1256,8 +1279,8 @@
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1272,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,70 +1336,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>800</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
-        <v>800</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="L17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="Q17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1200</v>
       </c>
       <c r="X17" s="3">
         <v>1200</v>
@@ -1381,79 +1408,85 @@
       <c r="Y17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="L18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1100</v>
       </c>
       <c r="X18" s="3">
         <v>-1100</v>
       </c>
       <c r="Y18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,31 +1512,32 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1550,102 +1584,108 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="W21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Z21" s="3">
         <v>-1100</v>
       </c>
-      <c r="R21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-1100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1692,102 +1732,108 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-1200</v>
       </c>
       <c r="Y23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-1200</v>
       </c>
       <c r="Y26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2163,11 +2224,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>1500</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2175,13 +2236,13 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>100</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
+      <c r="W29" s="3">
+        <v>100</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,31 +2398,34 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2402,79 +2472,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E38" s="2">
         <v>45443</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44804</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44712</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44620</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44074</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43982</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43890</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43799</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43708</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43616</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,87 +2831,91 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E41" s="3">
         <v>8500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>700</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1300</v>
       </c>
       <c r="W41" s="3">
         <v>1300</v>
       </c>
       <c r="X41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
@@ -2834,7 +2924,7 @@
         <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
         <v>300</v>
@@ -2849,23 +2939,23 @@
         <v>300</v>
       </c>
       <c r="M42" s="3">
+        <v>300</v>
+      </c>
+      <c r="N42" s="3">
         <v>600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -2879,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X42" s="3">
         <v>100</v>
@@ -2887,8 +2977,11 @@
       <c r="Y42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2896,70 +2989,73 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
-        <v>200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
-      </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
       </c>
       <c r="M43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>500</v>
       </c>
       <c r="O43" s="3">
+        <v>500</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>200</v>
-      </c>
-      <c r="V43" s="3">
-        <v>300</v>
       </c>
       <c r="W43" s="3">
         <v>300</v>
       </c>
       <c r="X43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2972,14 +3068,14 @@
       <c r="F44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3000,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>100</v>
@@ -3024,67 +3120,70 @@
         <v>100</v>
       </c>
       <c r="X44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y44" s="3">
         <v>200</v>
       </c>
-      <c r="Y44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>200</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>100</v>
-      </c>
       <c r="U45" s="3">
         <v>100</v>
       </c>
@@ -3100,90 +3199,96 @@
       <c r="Y45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E46" s="3">
         <v>9100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3203,8 +3308,8 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3212,15 +3317,15 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="3">
         <v>400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3236,14 +3341,17 @@
       <c r="W47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3260,13 +3368,13 @@
         <v>400</v>
       </c>
       <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>400</v>
       </c>
       <c r="K48" s="3">
         <v>400</v>
@@ -3278,7 +3386,7 @@
         <v>400</v>
       </c>
       <c r="N48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O48" s="3">
         <v>500</v>
@@ -3290,19 +3398,19 @@
         <v>500</v>
       </c>
       <c r="R48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S48" s="3">
         <v>600</v>
       </c>
       <c r="T48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
       </c>
       <c r="V48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W48" s="3">
         <v>600</v>
@@ -3311,10 +3419,13 @@
         <v>600</v>
       </c>
       <c r="Y48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3343,7 +3454,7 @@
         <v>500</v>
       </c>
       <c r="L49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M49" s="3">
         <v>400</v>
@@ -3358,7 +3469,7 @@
         <v>400</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
@@ -3379,13 +3490,16 @@
         <v>300</v>
       </c>
       <c r="X49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,16 +3643,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -3546,11 +3666,11 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E54" s="3">
         <v>10000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>2700</v>
       </c>
       <c r="W54" s="3">
         <v>2700</v>
       </c>
       <c r="X54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y54" s="3">
         <v>3500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,34 +3923,35 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -3829,19 +3960,19 @@
         <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
-        <v>100</v>
-      </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>100</v>
-      </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3850,22 +3981,25 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3911,8 +4045,8 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>10</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
@@ -3929,37 +4063,40 @@
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
+      <c r="E59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -3977,19 +4114,19 @@
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>200</v>
       </c>
       <c r="S59" s="3">
         <v>200</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -3998,42 +4135,45 @@
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>200</v>
       </c>
-      <c r="E60" s="3">
-        <v>100</v>
-      </c>
       <c r="F60" s="3">
         <v>100</v>
       </c>
       <c r="G60" s="3">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3">
         <v>300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>200</v>
       </c>
       <c r="L60" s="3">
         <v>200</v>
@@ -4051,16 +4191,16 @@
         <v>200</v>
       </c>
       <c r="Q60" s="3">
+        <v>200</v>
+      </c>
+      <c r="R60" s="3">
         <v>400</v>
-      </c>
-      <c r="R60" s="3">
-        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>200</v>
       </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
@@ -4069,36 +4209,39 @@
         <v>100</v>
       </c>
       <c r="W60" s="3">
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="X60" s="3">
-        <v>100</v>
-      </c>
       <c r="Y60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -4148,31 +4291,34 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4190,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -4201,8 +4347,8 @@
       <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>10</v>
+      <c r="T62" s="3">
+        <v>100</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>10</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,31 +4587,34 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>10</v>
+      <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>200</v>
       </c>
       <c r="G66" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H66" s="3">
-        <v>800</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>10</v>
+        <v>400</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>10</v>
@@ -4467,44 +4625,47 @@
       <c r="M66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N66" s="3">
-        <v>100</v>
+      <c r="N66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>300</v>
       </c>
       <c r="S66" s="3">
         <v>300</v>
       </c>
       <c r="T66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U66" s="3">
         <v>100</v>
       </c>
       <c r="V66" s="3">
+        <v>100</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
-      </c>
-      <c r="W66" s="3">
-        <v>300</v>
       </c>
       <c r="X66" s="3">
         <v>300</v>
       </c>
       <c r="Y66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-49400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-47600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-46900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-44500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-40900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-37600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-27100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-25700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-24800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-23900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-22800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E80" s="2">
         <v>45443</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44804</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44712</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44620</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44074</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43982</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43890</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43799</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43708</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43616</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5429,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -5471,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,28 +6054,31 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-5900</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1200</v>
       </c>
       <c r="J89" s="3">
         <v>-1200</v>
@@ -5870,13 +6087,13 @@
         <v>-1200</v>
       </c>
       <c r="L89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="M89" s="3">
         <v>-1300</v>
       </c>
       <c r="N89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="O89" s="3">
         <v>-1200</v>
@@ -5885,34 +6102,37 @@
         <v>-1200</v>
       </c>
       <c r="Q89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-600</v>
       </c>
       <c r="T89" s="3">
         <v>-600</v>
       </c>
       <c r="U89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-700</v>
       </c>
       <c r="W89" s="3">
         <v>-700</v>
       </c>
       <c r="X89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,49 +6158,50 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>10</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>10</v>
@@ -5994,23 +6215,26 @@
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,25 +6378,28 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -6178,29 +6408,29 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -6217,13 +6447,16 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,31 +6776,34 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1800</v>
       </c>
-      <c r="G100" s="3">
-        <v>1600</v>
-      </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -6572,51 +6818,54 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>4000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>9400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
       <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -6636,8 +6885,8 @@
       <c r="L101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
-        <v>-4500</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1300</v>
       </c>
       <c r="J102" s="3">
         <v>-1300</v>
       </c>
       <c r="K102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-1300</v>
       </c>
       <c r="M102" s="3">
         <v>-1300</v>
       </c>
       <c r="N102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,123 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E7" s="2">
         <v>45535</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45351</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45077</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44804</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44712</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44620</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44074</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43982</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43890</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43799</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43708</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43616</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -781,19 +784,19 @@
         <v>100</v>
       </c>
       <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
@@ -802,7 +805,7 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -811,51 +814,54 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
       <c r="S8" s="3">
+        <v>200</v>
+      </c>
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
-        <v>100</v>
-      </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -885,25 +891,25 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>0</v>
@@ -914,13 +920,16 @@
       <c r="Z9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -932,16 +941,16 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>100</v>
@@ -950,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -959,37 +968,40 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>200</v>
       </c>
       <c r="T10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
-      </c>
-      <c r="R12" s="3">
-        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>200</v>
       </c>
       <c r="T12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
-        <v>100</v>
-      </c>
       <c r="X12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="3">
         <v>200</v>
       </c>
       <c r="Z12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,22 +1198,22 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1208,8 +1227,8 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1238,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1256,16 +1278,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>10</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -1282,8 +1304,8 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1298,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,73 +1362,74 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>1200</v>
       </c>
       <c r="Y17" s="3">
         <v>1200</v>
@@ -1411,82 +1437,88 @@
       <c r="Z17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y18" s="3">
         <v>-1100</v>
       </c>
       <c r="Z18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1539,8 +1572,8 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1587,82 +1620,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1672,11 +1711,11 @@
       <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
@@ -1687,8 +1726,8 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1735,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1200</v>
       </c>
       <c r="H23" s="3">
         <v>-1200</v>
       </c>
       <c r="I23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1200</v>
       </c>
       <c r="Z23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1835,8 +1880,8 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1883,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1200</v>
       </c>
       <c r="H26" s="3">
         <v>-1200</v>
       </c>
       <c r="I26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-1200</v>
       </c>
       <c r="Z26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1200</v>
       </c>
       <c r="H27" s="3">
         <v>-1200</v>
       </c>
       <c r="I27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2227,11 +2287,11 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>1500</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -2239,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
+      <c r="X29" s="3">
+        <v>100</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2427,8 +2496,8 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2475,82 +2544,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1200</v>
       </c>
       <c r="H33" s="3">
         <v>-1200</v>
       </c>
       <c r="I33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1200</v>
       </c>
       <c r="H35" s="3">
         <v>-1200</v>
       </c>
       <c r="I35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E38" s="2">
         <v>45535</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45351</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45077</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44804</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44712</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44074</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43982</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43890</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43799</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43708</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43616</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,93 +2917,97 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E41" s="3">
         <v>6500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1300</v>
       </c>
       <c r="X41" s="3">
         <v>1300</v>
       </c>
       <c r="Y41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
@@ -2927,7 +3016,7 @@
         <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>300</v>
@@ -2942,23 +3031,23 @@
         <v>300</v>
       </c>
       <c r="N42" s="3">
+        <v>300</v>
+      </c>
+      <c r="O42" s="3">
         <v>600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>500</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
@@ -2972,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>100</v>
@@ -2980,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
-        <v>100</v>
-      </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
       <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
-      </c>
-      <c r="L43" s="3">
-        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="O43" s="3">
         <v>500</v>
       </c>
       <c r="P43" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
-      </c>
-      <c r="W43" s="3">
-        <v>300</v>
       </c>
       <c r="X43" s="3">
         <v>300</v>
       </c>
       <c r="Y43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3077,8 +3172,8 @@
       <c r="I44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3099,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -3123,13 +3218,16 @@
         <v>100</v>
       </c>
       <c r="Y44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z44" s="3">
         <v>200</v>
       </c>
-      <c r="Z44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3154,39 +3252,39 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
-        <v>100</v>
-      </c>
       <c r="V45" s="3">
         <v>100</v>
       </c>
@@ -3202,82 +3300,88 @@
       <c r="Z45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3311,8 +3415,8 @@
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3320,15 +3424,15 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3344,14 +3448,17 @@
       <c r="X47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3371,13 +3478,13 @@
         <v>400</v>
       </c>
       <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>400</v>
@@ -3389,7 +3496,7 @@
         <v>400</v>
       </c>
       <c r="O48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P48" s="3">
         <v>500</v>
@@ -3401,19 +3508,19 @@
         <v>500</v>
       </c>
       <c r="S48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T48" s="3">
         <v>600</v>
       </c>
       <c r="U48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="V48" s="3">
         <v>500</v>
       </c>
       <c r="W48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X48" s="3">
         <v>600</v>
@@ -3422,10 +3529,13 @@
         <v>600</v>
       </c>
       <c r="Z48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3457,7 +3567,7 @@
         <v>500</v>
       </c>
       <c r="M49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N49" s="3">
         <v>400</v>
@@ -3472,7 +3582,7 @@
         <v>400</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
@@ -3493,13 +3603,16 @@
         <v>300</v>
       </c>
       <c r="Y49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3658,7 +3777,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -3666,14 +3785,14 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>10</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2000</v>
-      </c>
-      <c r="W54" s="3">
-        <v>2700</v>
       </c>
       <c r="X54" s="3">
         <v>2700</v>
       </c>
       <c r="Y54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Z54" s="3">
         <v>3500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,37 +4053,38 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
-        <v>100</v>
-      </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -3963,19 +4093,19 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
-        <v>100</v>
-      </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3984,22 +4114,25 @@
         <v>0</v>
       </c>
       <c r="V57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4048,8 +4181,8 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>10</v>
@@ -4066,22 +4199,25 @@
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>10</v>
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>10</v>
@@ -4095,11 +4231,11 @@
       <c r="I59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="J59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -4117,19 +4253,19 @@
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>200</v>
       </c>
       <c r="T59" s="3">
         <v>200</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -4138,45 +4274,48 @@
         <v>0</v>
       </c>
       <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>200</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>200</v>
       </c>
-      <c r="F60" s="3">
-        <v>100</v>
-      </c>
       <c r="G60" s="3">
         <v>100</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
-      </c>
-      <c r="L60" s="3">
-        <v>200</v>
       </c>
       <c r="M60" s="3">
         <v>200</v>
@@ -4194,16 +4333,16 @@
         <v>200</v>
       </c>
       <c r="R60" s="3">
+        <v>200</v>
+      </c>
+      <c r="S60" s="3">
         <v>400</v>
-      </c>
-      <c r="S60" s="3">
-        <v>200</v>
       </c>
       <c r="T60" s="3">
         <v>200</v>
       </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
@@ -4212,16 +4351,19 @@
         <v>100</v>
       </c>
       <c r="X60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3">
-        <v>100</v>
-      </c>
       <c r="Z60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4244,7 +4386,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4294,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4320,8 +4465,8 @@
       <c r="J62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4339,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
@@ -4350,8 +4495,8 @@
       <c r="T62" s="3">
         <v>100</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>10</v>
+      <c r="U62" s="3">
+        <v>100</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>10</v>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,35 +4744,38 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4628,44 +4785,47 @@
       <c r="N66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O66" s="3">
-        <v>100</v>
+      <c r="O66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>400</v>
-      </c>
-      <c r="S66" s="3">
-        <v>300</v>
       </c>
       <c r="T66" s="3">
         <v>300</v>
       </c>
       <c r="U66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
       </c>
       <c r="W66" s="3">
+        <v>100</v>
+      </c>
+      <c r="X66" s="3">
         <v>200</v>
-      </c>
-      <c r="X66" s="3">
-        <v>300</v>
       </c>
       <c r="Y66" s="3">
         <v>300</v>
       </c>
       <c r="Z66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-49400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-47600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-46900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-42200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-40900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-37600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-33800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-27800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-27100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-25700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-24800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-22800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E80" s="2">
         <v>45535</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45351</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45077</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44804</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44712</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44620</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44074</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43982</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43890</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43799</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43708</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43616</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1200</v>
       </c>
       <c r="H81" s="3">
         <v>-1200</v>
       </c>
       <c r="I81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5673,10 +5871,10 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,31 +6270,34 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1200</v>
       </c>
       <c r="K89" s="3">
         <v>-1200</v>
@@ -6090,13 +6306,13 @@
         <v>-1200</v>
       </c>
       <c r="M89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="N89" s="3">
         <v>-1300</v>
       </c>
       <c r="O89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="P89" s="3">
         <v>-1200</v>
@@ -6105,34 +6321,37 @@
         <v>-1200</v>
       </c>
       <c r="R89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-600</v>
       </c>
       <c r="U89" s="3">
         <v>-600</v>
       </c>
       <c r="V89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-700</v>
       </c>
       <c r="X89" s="3">
         <v>-700</v>
       </c>
       <c r="Y89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,16 +6378,17 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>10</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>10</v>
@@ -6176,8 +6396,8 @@
       <c r="G91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -6189,22 +6409,22 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>10</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>10</v>
@@ -6218,23 +6438,26 @@
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,29 +6607,32 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -6411,29 +6640,29 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -6450,13 +6679,16 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,34 +7021,37 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6821,45 +7066,48 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>4000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>9400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>10</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>10</v>
@@ -6888,8 +7136,8 @@
       <c r="M101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6927,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1300</v>
       </c>
       <c r="K102" s="3">
         <v>-1300</v>
       </c>
       <c r="L102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-1300</v>
       </c>
       <c r="N102" s="3">
         <v>-1300</v>
       </c>
       <c r="O102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E7" s="2">
         <v>45626</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45535</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45443</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45351</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45260</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45169</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45077</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44985</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44895</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44804</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44712</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44530</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44439</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44347</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44255</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44165</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44074</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43982</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43890</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43799</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43708</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43616</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,7 +782,7 @@
         <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -787,19 +791,19 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
@@ -808,7 +812,7 @@
         <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -817,54 +821,57 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>200</v>
       </c>
       <c r="T8" s="3">
+        <v>200</v>
+      </c>
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
-        <v>100</v>
-      </c>
       <c r="V8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3">
         <v>100</v>
       </c>
       <c r="AA8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -894,25 +901,25 @@
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>0</v>
@@ -923,8 +930,11 @@
       <c r="AA9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -932,7 +942,7 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -944,16 +954,16 @@
         <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
@@ -962,7 +972,7 @@
         <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>0</v>
@@ -971,37 +981,40 @@
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
-      </c>
-      <c r="S12" s="3">
-        <v>200</v>
       </c>
       <c r="T12" s="3">
         <v>200</v>
       </c>
       <c r="U12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="X12" s="3">
-        <v>100</v>
-      </c>
       <c r="Y12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="3">
         <v>200</v>
       </c>
       <c r="AA12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,22 +1221,22 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
@@ -1230,8 +1250,8 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1260,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1281,16 +1304,16 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>10</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>10</v>
@@ -1307,8 +1330,8 @@
       <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1323,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,8 +1389,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1372,67 +1399,67 @@
         <v>2900</v>
       </c>
       <c r="E17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1200</v>
       </c>
       <c r="Z17" s="3">
         <v>1200</v>
@@ -1440,85 +1467,91 @@
       <c r="AA17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z18" s="3">
         <v>-1100</v>
       </c>
       <c r="AA18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1575,8 +1609,8 @@
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1623,8 +1657,11 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1632,76 +1669,79 @@
         <v>-2700</v>
       </c>
       <c r="E21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1714,11 +1754,11 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
@@ -1729,8 +1769,8 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1777,8 +1817,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1786,76 +1829,79 @@
         <v>-2700</v>
       </c>
       <c r="E23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1200</v>
       </c>
       <c r="I23" s="3">
         <v>-1200</v>
       </c>
       <c r="J23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-1200</v>
       </c>
       <c r="AA23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1883,8 +1929,8 @@
       <c r="K24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2017,76 +2069,79 @@
         <v>-2700</v>
       </c>
       <c r="E26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1200</v>
       </c>
       <c r="I26" s="3">
         <v>-1200</v>
       </c>
       <c r="J26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-1200</v>
       </c>
       <c r="AA26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2094,76 +2149,79 @@
         <v>-2700</v>
       </c>
       <c r="E27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1200</v>
       </c>
       <c r="I27" s="3">
         <v>-1200</v>
       </c>
       <c r="J27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2290,11 +2351,11 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>1500</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2302,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X29" s="3">
         <v>100</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>100</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2499,8 +2569,8 @@
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2547,8 +2617,11 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2556,76 +2629,79 @@
         <v>-2700</v>
       </c>
       <c r="E33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1200</v>
       </c>
       <c r="I33" s="3">
         <v>-1200</v>
       </c>
       <c r="J33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,8 +2777,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2710,158 +2789,164 @@
         <v>-2700</v>
       </c>
       <c r="E35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1200</v>
       </c>
       <c r="I35" s="3">
         <v>-1200</v>
       </c>
       <c r="J35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E38" s="2">
         <v>45626</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45535</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45443</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45351</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45260</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45169</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45077</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44985</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44895</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44804</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44712</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44530</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44439</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44347</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44255</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44165</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44074</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43982</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43890</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43799</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43708</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43616</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,99 +3004,103 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E41" s="3">
         <v>8100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
-      </c>
-      <c r="X41" s="3">
-        <v>1300</v>
       </c>
       <c r="Y41" s="3">
         <v>1300</v>
       </c>
       <c r="Z41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
@@ -3019,7 +3109,7 @@
         <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>300</v>
@@ -3034,23 +3124,23 @@
         <v>300</v>
       </c>
       <c r="O42" s="3">
+        <v>300</v>
+      </c>
+      <c r="P42" s="3">
         <v>600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>500</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
@@ -3064,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3">
         <v>100</v>
@@ -3072,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3081,76 +3174,79 @@
         <v>300</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
-        <v>100</v>
-      </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
       <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
-      </c>
-      <c r="M43" s="3">
-        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
       </c>
       <c r="O43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="P43" s="3">
         <v>500</v>
       </c>
       <c r="Q43" s="3">
+        <v>500</v>
+      </c>
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
-      </c>
-      <c r="X43" s="3">
-        <v>300</v>
       </c>
       <c r="Y43" s="3">
         <v>300</v>
       </c>
       <c r="Z43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3175,8 +3271,8 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3197,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>100</v>
@@ -3221,13 +3317,16 @@
         <v>100</v>
       </c>
       <c r="Z44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA44" s="3">
         <v>200</v>
       </c>
-      <c r="AA44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3255,39 +3354,39 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
-        <v>100</v>
-      </c>
       <c r="W45" s="3">
         <v>100</v>
       </c>
@@ -3303,85 +3402,91 @@
       <c r="AA45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E46" s="3">
         <v>8800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3418,8 +3523,8 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3427,15 +3532,15 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3451,14 +3556,17 @@
       <c r="Y47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3481,13 +3589,13 @@
         <v>400</v>
       </c>
       <c r="J48" s="3">
+        <v>400</v>
+      </c>
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>400</v>
       </c>
       <c r="M48" s="3">
         <v>400</v>
@@ -3499,7 +3607,7 @@
         <v>400</v>
       </c>
       <c r="P48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q48" s="3">
         <v>500</v>
@@ -3511,19 +3619,19 @@
         <v>500</v>
       </c>
       <c r="T48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>600</v>
       </c>
       <c r="V48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W48" s="3">
         <v>500</v>
       </c>
       <c r="X48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y48" s="3">
         <v>600</v>
@@ -3532,10 +3640,13 @@
         <v>600</v>
       </c>
       <c r="AA48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3570,7 +3681,7 @@
         <v>500</v>
       </c>
       <c r="N49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O49" s="3">
         <v>400</v>
@@ -3585,7 +3696,7 @@
         <v>400</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
@@ -3606,13 +3717,16 @@
         <v>300</v>
       </c>
       <c r="Z49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3780,7 +3900,7 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -3788,14 +3908,14 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>10</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E54" s="3">
         <v>9800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2000</v>
-      </c>
-      <c r="X54" s="3">
-        <v>2700</v>
       </c>
       <c r="Y54" s="3">
         <v>2700</v>
       </c>
       <c r="Z54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AA54" s="3">
         <v>3500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,40 +4184,41 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
-        <v>100</v>
-      </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -4096,19 +4227,19 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>100</v>
-      </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
-        <v>100</v>
-      </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4117,22 +4248,25 @@
         <v>0</v>
       </c>
       <c r="W57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4184,8 +4318,8 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>10</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>10</v>
@@ -4202,25 +4336,28 @@
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>10</v>
+      <c r="E59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -4234,11 +4371,11 @@
       <c r="J59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3">
         <v>100</v>
@@ -4256,19 +4393,19 @@
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>300</v>
-      </c>
-      <c r="T59" s="3">
-        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>200</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4277,48 +4414,51 @@
         <v>0</v>
       </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>200</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
       <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E60" s="3">
         <v>300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>200</v>
       </c>
-      <c r="G60" s="3">
-        <v>100</v>
-      </c>
       <c r="H60" s="3">
         <v>100</v>
       </c>
       <c r="I60" s="3">
+        <v>100</v>
+      </c>
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>200</v>
       </c>
       <c r="N60" s="3">
         <v>200</v>
@@ -4336,16 +4476,16 @@
         <v>200</v>
       </c>
       <c r="S60" s="3">
+        <v>200</v>
+      </c>
+      <c r="T60" s="3">
         <v>400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>200</v>
       </c>
       <c r="U60" s="3">
         <v>200</v>
       </c>
       <c r="V60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W60" s="3">
         <v>100</v>
@@ -4354,16 +4494,19 @@
         <v>100</v>
       </c>
       <c r="Y60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z60" s="3">
         <v>200</v>
       </c>
-      <c r="Z60" s="3">
-        <v>100</v>
-      </c>
       <c r="AA60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4389,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4468,8 +4614,8 @@
       <c r="K62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4487,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -4498,8 +4644,8 @@
       <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>10</v>
+      <c r="V62" s="3">
+        <v>100</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>10</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,38 +4902,41 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E66" s="3">
         <v>400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4788,44 +4946,47 @@
       <c r="O66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P66" s="3">
-        <v>100</v>
+      <c r="P66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R66" s="3">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>400</v>
-      </c>
-      <c r="T66" s="3">
-        <v>300</v>
       </c>
       <c r="U66" s="3">
         <v>300</v>
       </c>
       <c r="V66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="W66" s="3">
         <v>100</v>
       </c>
       <c r="X66" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y66" s="3">
         <v>200</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>300</v>
       </c>
       <c r="Z66" s="3">
         <v>300</v>
       </c>
       <c r="AA66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-51600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-49400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-46900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-42200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-40900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-39100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-37600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-31800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-28500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-27800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-25700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-22800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E76" s="3">
         <v>9800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,90 +5812,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E80" s="2">
         <v>45626</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45535</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45443</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45351</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45260</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45169</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45077</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44985</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44895</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44804</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44712</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44530</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44439</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44347</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44255</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44165</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44074</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43982</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43890</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43799</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43708</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43616</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5714,76 +5909,79 @@
         <v>-2700</v>
       </c>
       <c r="E81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1200</v>
       </c>
       <c r="I81" s="3">
         <v>-1200</v>
       </c>
       <c r="J81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5874,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,34 +6487,37 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
       </c>
       <c r="L89" s="3">
         <v>-1200</v>
@@ -6309,13 +6526,13 @@
         <v>-1200</v>
       </c>
       <c r="N89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="O89" s="3">
         <v>-1300</v>
       </c>
       <c r="P89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Q89" s="3">
         <v>-1200</v>
@@ -6324,34 +6541,37 @@
         <v>-1200</v>
       </c>
       <c r="S89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-600</v>
       </c>
       <c r="V89" s="3">
         <v>-600</v>
       </c>
       <c r="W89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-700</v>
       </c>
       <c r="Y89" s="3">
         <v>-700</v>
       </c>
       <c r="Z89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6390,8 +6611,8 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -6399,8 +6620,8 @@
       <c r="H91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6412,22 +6633,22 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>10</v>
@@ -6441,23 +6662,26 @@
       <c r="V91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6619,23 +6849,23 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -6643,29 +6873,29 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -6682,13 +6912,16 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,37 +7267,40 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>4300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -7069,48 +7315,51 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>4000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>9400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
-        <v>100</v>
-      </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>10</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>10</v>
@@ -7139,8 +7388,8 @@
       <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1300</v>
       </c>
       <c r="L102" s="3">
         <v>-1300</v>
       </c>
       <c r="M102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-1300</v>
       </c>
       <c r="O102" s="3">
         <v>-1300</v>
       </c>
       <c r="P102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E7" s="2">
         <v>45716</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45626</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45535</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45443</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45351</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45260</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45169</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45077</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44985</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44895</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44804</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44712</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44620</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44530</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44439</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44347</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44255</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44165</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44074</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43982</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43890</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43799</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43708</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43616</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,7 +789,7 @@
         <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
@@ -794,19 +798,19 @@
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
@@ -815,7 +819,7 @@
         <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -824,57 +828,60 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3">
         <v>200</v>
       </c>
       <c r="U8" s="3">
+        <v>200</v>
+      </c>
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
-        <v>100</v>
-      </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>100</v>
       </c>
       <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -904,25 +911,25 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
         <v>0</v>
@@ -933,8 +940,11 @@
       <c r="AB9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -945,7 +955,7 @@
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -957,16 +967,16 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
@@ -975,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
@@ -984,37 +994,40 @@
         <v>0</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
         <v>200</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3">
         <v>100</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>500</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>200</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
         <v>300</v>
       </c>
-      <c r="Y12" s="3">
-        <v>100</v>
-      </c>
       <c r="Z12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
         <v>200</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,22 +1244,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
@@ -1253,8 +1273,8 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1307,16 +1330,16 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>10</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>10</v>
@@ -1333,8 +1356,8 @@
       <c r="R15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1349,10 +1372,10 @@
         <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,79 +1416,80 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="E17" s="3">
         <v>2900</v>
       </c>
       <c r="F17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>1200</v>
       </c>
       <c r="AA17" s="3">
         <v>1200</v>
@@ -1470,88 +1497,94 @@
       <c r="AB17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA18" s="3">
         <v>-1100</v>
       </c>
       <c r="AB18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1612,8 +1646,8 @@
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1660,88 +1694,94 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2700</v>
+        <v>-3700</v>
       </c>
       <c r="E21" s="3">
         <v>-2700</v>
       </c>
       <c r="F21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1757,11 +1797,11 @@
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
@@ -1772,8 +1812,8 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1820,88 +1860,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E23" s="3">
         <v>-2700</v>
       </c>
       <c r="F23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1200</v>
       </c>
       <c r="J23" s="3">
         <v>-1200</v>
       </c>
       <c r="K23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-1200</v>
       </c>
       <c r="AB23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +1978,8 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E26" s="3">
         <v>-2700</v>
       </c>
       <c r="F26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1200</v>
       </c>
       <c r="J26" s="3">
         <v>-1200</v>
       </c>
       <c r="K26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-1200</v>
       </c>
       <c r="AB26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E27" s="3">
         <v>-2700</v>
       </c>
       <c r="F27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1200</v>
       </c>
       <c r="J27" s="3">
         <v>-1200</v>
       </c>
       <c r="K27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2354,11 +2415,11 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>1500</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2366,13 +2427,13 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
+      <c r="Z29" s="3">
+        <v>100</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2572,8 +2642,8 @@
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2620,88 +2690,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E33" s="3">
         <v>-2700</v>
       </c>
       <c r="F33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1200</v>
       </c>
       <c r="J33" s="3">
         <v>-1200</v>
       </c>
       <c r="K33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E35" s="3">
         <v>-2700</v>
       </c>
       <c r="F35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1200</v>
       </c>
       <c r="J35" s="3">
         <v>-1200</v>
       </c>
       <c r="K35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E38" s="2">
         <v>45716</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45626</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45535</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45443</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45351</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45260</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45169</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45077</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44985</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44895</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44804</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44712</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44620</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44530</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44439</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44347</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44255</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44165</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44074</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43982</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43890</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43799</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43708</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43616</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,105 +3091,109 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E41" s="3">
         <v>6500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>700</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>1300</v>
       </c>
       <c r="Z41" s="3">
         <v>1300</v>
       </c>
       <c r="AA41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB41" s="3">
         <v>2000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>100</v>
@@ -3112,7 +3202,7 @@
         <v>100</v>
       </c>
       <c r="K42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L42" s="3">
         <v>300</v>
@@ -3127,23 +3217,23 @@
         <v>300</v>
       </c>
       <c r="P42" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q42" s="3">
         <v>600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>500</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
@@ -3157,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="3">
         <v>100</v>
@@ -3165,88 +3255,94 @@
       <c r="AB42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
         <v>300</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
       <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
-        <v>100</v>
-      </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>200</v>
       </c>
       <c r="O43" s="3">
         <v>200</v>
       </c>
       <c r="P43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Q43" s="3">
         <v>500</v>
       </c>
       <c r="R43" s="3">
+        <v>500</v>
+      </c>
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>300</v>
       </c>
       <c r="Z43" s="3">
         <v>300</v>
       </c>
       <c r="AA43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,8 +3370,8 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3296,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
@@ -3320,13 +3416,16 @@
         <v>100</v>
       </c>
       <c r="AA44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB44" s="3">
         <v>200</v>
       </c>
-      <c r="AB44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3357,39 +3456,39 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
-        <v>100</v>
-      </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
@@ -3405,88 +3504,94 @@
       <c r="AB45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3526,8 +3631,8 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3535,15 +3640,15 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U47" s="3">
         <v>400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3559,14 +3664,17 @@
       <c r="Z47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3592,13 +3700,13 @@
         <v>400</v>
       </c>
       <c r="K48" s="3">
+        <v>400</v>
+      </c>
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>400</v>
@@ -3610,7 +3718,7 @@
         <v>400</v>
       </c>
       <c r="Q48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>500</v>
@@ -3622,19 +3730,19 @@
         <v>500</v>
       </c>
       <c r="U48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="V48" s="3">
         <v>600</v>
       </c>
       <c r="W48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="X48" s="3">
         <v>500</v>
       </c>
       <c r="Y48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z48" s="3">
         <v>600</v>
@@ -3643,10 +3751,13 @@
         <v>600</v>
       </c>
       <c r="AB48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3684,7 +3795,7 @@
         <v>500</v>
       </c>
       <c r="O49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>400</v>
@@ -3699,7 +3810,7 @@
         <v>400</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
@@ -3720,13 +3831,16 @@
         <v>300</v>
       </c>
       <c r="AA49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3903,7 +4023,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -3911,14 +4031,14 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>10</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2000</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>2700</v>
       </c>
       <c r="Z54" s="3">
         <v>2700</v>
       </c>
       <c r="AA54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB54" s="3">
         <v>3500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,43 +4315,44 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -4230,19 +4361,19 @@
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
-        <v>100</v>
-      </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
-        <v>100</v>
-      </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -4251,22 +4382,25 @@
         <v>0</v>
       </c>
       <c r="X57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4321,8 +4455,8 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>10</v>
@@ -4339,14 +4473,17 @@
       <c r="Z58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4356,11 +4493,11 @@
       <c r="E59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="F59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -4374,11 +4511,11 @@
       <c r="K59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
@@ -4396,19 +4533,19 @@
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>300</v>
-      </c>
-      <c r="U59" s="3">
-        <v>200</v>
       </c>
       <c r="V59" s="3">
         <v>200</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -4417,51 +4554,54 @@
         <v>0</v>
       </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
         <v>200</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
       <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
-        <v>100</v>
-      </c>
       <c r="I60" s="3">
         <v>100</v>
       </c>
       <c r="J60" s="3">
+        <v>100</v>
+      </c>
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>200</v>
       </c>
       <c r="O60" s="3">
         <v>200</v>
@@ -4479,16 +4619,16 @@
         <v>200</v>
       </c>
       <c r="T60" s="3">
+        <v>200</v>
+      </c>
+      <c r="U60" s="3">
         <v>400</v>
-      </c>
-      <c r="U60" s="3">
-        <v>200</v>
       </c>
       <c r="V60" s="3">
         <v>200</v>
       </c>
       <c r="W60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X60" s="3">
         <v>100</v>
@@ -4497,16 +4637,19 @@
         <v>100</v>
       </c>
       <c r="Z60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="3">
         <v>200</v>
       </c>
-      <c r="AA60" s="3">
-        <v>100</v>
-      </c>
       <c r="AB60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4535,7 +4678,7 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4617,8 +4763,8 @@
       <c r="L62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4636,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -4647,8 +4793,8 @@
       <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>10</v>
+      <c r="W62" s="3">
+        <v>100</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>10</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,41 +5060,44 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4949,44 +5107,47 @@
       <c r="P66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q66" s="3">
-        <v>100</v>
+      <c r="Q66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S66" s="3">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>400</v>
-      </c>
-      <c r="U66" s="3">
-        <v>300</v>
       </c>
       <c r="V66" s="3">
         <v>300</v>
       </c>
       <c r="W66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X66" s="3">
         <v>100</v>
       </c>
       <c r="Y66" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z66" s="3">
         <v>200</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>300</v>
       </c>
       <c r="AA66" s="3">
         <v>300</v>
       </c>
       <c r="AB66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-57000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-54300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-46900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-44500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-42200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-40900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-39100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-37600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-33800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-31800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-30700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-28100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-28500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-27100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E80" s="2">
         <v>45716</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45626</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45535</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45443</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45351</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45260</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45169</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45077</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44985</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44895</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44804</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44712</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44620</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44530</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44439</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44347</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44255</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44165</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44074</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43982</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43890</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43799</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43708</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43616</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2700</v>
+        <v>-3800</v>
       </c>
       <c r="E81" s="3">
         <v>-2700</v>
       </c>
       <c r="F81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1200</v>
       </c>
       <c r="J81" s="3">
         <v>-1200</v>
       </c>
       <c r="K81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6076,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,37 +6704,40 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1200</v>
       </c>
       <c r="M89" s="3">
         <v>-1200</v>
@@ -6529,13 +6746,13 @@
         <v>-1200</v>
       </c>
       <c r="O89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="P89" s="3">
         <v>-1300</v>
       </c>
       <c r="Q89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="R89" s="3">
         <v>-1200</v>
@@ -6544,34 +6761,37 @@
         <v>-1200</v>
       </c>
       <c r="T89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-600</v>
       </c>
       <c r="W89" s="3">
         <v>-600</v>
       </c>
       <c r="X89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-700</v>
       </c>
       <c r="Z89" s="3">
         <v>-700</v>
       </c>
       <c r="AA89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6614,8 +6835,8 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>10</v>
@@ -6623,8 +6844,8 @@
       <c r="I91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6636,22 +6857,22 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
@@ -6665,23 +6886,26 @@
       <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7067,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6852,23 +7082,23 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -6876,29 +7106,29 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -6915,13 +7145,16 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6982,8 +7216,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,40 +7513,43 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>4300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -7318,40 +7564,43 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>4000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>9400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
-        <v>100</v>
-      </c>
       <c r="AA100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7361,8 +7610,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -7391,8 +7640,8 @@
       <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-1300</v>
       </c>
       <c r="M102" s="3">
         <v>-1300</v>
       </c>
       <c r="N102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-1300</v>
       </c>
       <c r="P102" s="3">
         <v>-1300</v>
       </c>
       <c r="Q102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,138 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E7" s="2">
         <v>45900</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45716</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45626</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45535</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45443</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45351</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45260</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45169</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45077</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44985</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44895</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44804</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44712</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44620</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44530</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44439</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44347</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44255</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44165</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44074</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43982</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43890</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43799</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43708</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43616</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>200</v>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
@@ -799,7 +802,7 @@
         <v>200</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
@@ -808,19 +811,19 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
@@ -829,7 +832,7 @@
         <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -838,63 +841,66 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>200</v>
       </c>
       <c r="W8" s="3">
+        <v>200</v>
+      </c>
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
-        <v>100</v>
-      </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3">
         <v>100</v>
       </c>
       <c r="AD8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>10</v>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
+      <c r="K9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -924,25 +930,25 @@
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
@@ -953,13 +959,16 @@
       <c r="AD9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>200</v>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
@@ -971,7 +980,7 @@
         <v>200</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -983,16 +992,16 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
@@ -1001,7 +1010,7 @@
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
@@ -1010,37 +1019,40 @@
         <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="3">
         <v>100</v>
       </c>
       <c r="AD10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
-      </c>
-      <c r="V12" s="3">
-        <v>200</v>
       </c>
       <c r="W12" s="3">
         <v>200</v>
       </c>
       <c r="X12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
         <v>300</v>
       </c>
-      <c r="AA12" s="3">
-        <v>100</v>
-      </c>
       <c r="AB12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3">
         <v>200</v>
       </c>
       <c r="AD12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1252,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1270,22 +1289,22 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
@@ -1299,8 +1318,8 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1329,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1359,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>10</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>10</v>
@@ -1385,8 +1407,8 @@
       <c r="T15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1401,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,85 +1469,86 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2900</v>
+        <v>1600</v>
       </c>
       <c r="E17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2900</v>
       </c>
       <c r="G17" s="3">
         <v>2900</v>
       </c>
       <c r="H17" s="3">
-        <v>2200</v>
+        <v>2900</v>
       </c>
       <c r="I17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1200</v>
       </c>
       <c r="AC17" s="3">
         <v>1200</v>
@@ -1530,94 +1556,100 @@
       <c r="AD17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2100</v>
-      </c>
       <c r="I18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC18" s="3">
         <v>-1100</v>
       </c>
       <c r="AD18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1686,8 +1719,8 @@
       <c r="N20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1734,94 +1767,100 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2700</v>
+        <v>-1600</v>
       </c>
       <c r="E21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2700</v>
       </c>
       <c r="G21" s="3">
         <v>-2700</v>
       </c>
       <c r="H21" s="3">
-        <v>-2100</v>
+        <v>-2700</v>
       </c>
       <c r="I21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1843,11 +1882,11 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
@@ -1858,8 +1897,8 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1906,99 +1945,105 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-2700</v>
       </c>
       <c r="G23" s="3">
         <v>-2700</v>
       </c>
       <c r="H23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1200</v>
       </c>
       <c r="L23" s="3">
         <v>-1200</v>
       </c>
       <c r="M23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-1200</v>
       </c>
       <c r="AD23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>10</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>10</v>
@@ -2030,8 +2075,8 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2078,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-2700</v>
       </c>
       <c r="G26" s="3">
         <v>-2700</v>
       </c>
       <c r="H26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1200</v>
       </c>
       <c r="L26" s="3">
         <v>-1200</v>
       </c>
       <c r="M26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-1200</v>
       </c>
       <c r="AD26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-2700</v>
       </c>
       <c r="G27" s="3">
         <v>-2700</v>
       </c>
       <c r="H27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1200</v>
       </c>
       <c r="L27" s="3">
         <v>-1200</v>
       </c>
       <c r="M27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2482,11 +2542,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>1500</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2494,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
+      <c r="AB29" s="3">
+        <v>100</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2718,8 +2787,8 @@
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2766,94 +2835,100 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-2700</v>
       </c>
       <c r="G33" s="3">
         <v>-2700</v>
       </c>
       <c r="H33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1200</v>
       </c>
       <c r="L33" s="3">
         <v>-1200</v>
       </c>
       <c r="M33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-2700</v>
       </c>
       <c r="G35" s="3">
         <v>-2700</v>
       </c>
       <c r="H35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1200</v>
       </c>
       <c r="L35" s="3">
         <v>-1200</v>
       </c>
       <c r="M35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E38" s="2">
         <v>45900</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45808</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45716</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45626</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45535</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45443</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45351</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45260</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45169</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45077</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44985</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44895</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44804</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44712</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44620</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44530</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44439</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44347</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44255</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44165</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44074</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43982</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43890</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43799</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43708</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43616</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,117 +3264,121 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>1300</v>
       </c>
       <c r="AB41" s="3">
         <v>1300</v>
       </c>
       <c r="AC41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD41" s="3">
         <v>2000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -3298,7 +3387,7 @@
         <v>100</v>
       </c>
       <c r="M42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N42" s="3">
         <v>300</v>
@@ -3313,23 +3402,23 @@
         <v>300</v>
       </c>
       <c r="R42" s="3">
+        <v>300</v>
+      </c>
+      <c r="S42" s="3">
         <v>600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>500</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
@@ -3343,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="3">
         <v>100</v>
@@ -3351,94 +3440,100 @@
       <c r="AD42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
       </c>
       <c r="F43" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G43" s="3">
         <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
-        <v>100</v>
-      </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
-        <v>100</v>
-      </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>200</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
       </c>
       <c r="R43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="S43" s="3">
         <v>500</v>
       </c>
       <c r="T43" s="3">
+        <v>500</v>
+      </c>
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>200</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>300</v>
       </c>
       <c r="AB43" s="3">
         <v>300</v>
       </c>
       <c r="AC43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3472,8 +3567,8 @@
       <c r="M44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3494,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
         <v>100</v>
@@ -3518,13 +3613,16 @@
         <v>100</v>
       </c>
       <c r="AC44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD44" s="3">
         <v>200</v>
       </c>
-      <c r="AD44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3561,39 +3659,39 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
-        <v>100</v>
-      </c>
       <c r="Z45" s="3">
         <v>100</v>
       </c>
@@ -3609,94 +3707,100 @@
       <c r="AD45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
         <v>3500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3742,8 +3846,8 @@
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3751,15 +3855,15 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W47" s="3">
         <v>400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3775,14 +3879,17 @@
       <c r="AB47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3790,7 +3897,7 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>400</v>
@@ -3814,13 +3921,13 @@
         <v>400</v>
       </c>
       <c r="M48" s="3">
+        <v>400</v>
+      </c>
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>400</v>
       </c>
       <c r="P48" s="3">
         <v>400</v>
@@ -3832,7 +3939,7 @@
         <v>400</v>
       </c>
       <c r="S48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T48" s="3">
         <v>500</v>
@@ -3844,19 +3951,19 @@
         <v>500</v>
       </c>
       <c r="W48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X48" s="3">
         <v>600</v>
       </c>
       <c r="Y48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z48" s="3">
         <v>500</v>
       </c>
       <c r="AA48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AB48" s="3">
         <v>600</v>
@@ -3865,10 +3972,13 @@
         <v>600</v>
       </c>
       <c r="AD48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3876,7 +3986,7 @@
         <v>300</v>
       </c>
       <c r="E49" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F49" s="3">
         <v>500</v>
@@ -3912,7 +4022,7 @@
         <v>500</v>
       </c>
       <c r="Q49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>400</v>
@@ -3927,7 +4037,7 @@
         <v>400</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
@@ -3948,13 +4058,16 @@
         <v>300</v>
       </c>
       <c r="AC49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4149,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4157,14 +4276,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>10</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>2700</v>
       </c>
       <c r="AB54" s="3">
         <v>2700</v>
       </c>
       <c r="AC54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD54" s="3">
         <v>3500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,49 +4576,50 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
         <v>600</v>
       </c>
       <c r="F57" s="3">
+        <v>600</v>
+      </c>
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -4498,19 +4628,19 @@
         <v>100</v>
       </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
-        <v>100</v>
-      </c>
       <c r="U57" s="3">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
-        <v>100</v>
-      </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -4519,22 +4649,25 @@
         <v>0</v>
       </c>
       <c r="Z57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
       <c r="AB57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4595,8 +4728,8 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
@@ -4613,14 +4746,17 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4636,11 +4772,11 @@
       <c r="G59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>10</v>
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>10</v>
@@ -4654,11 +4790,11 @@
       <c r="M59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3">
         <v>100</v>
@@ -4676,19 +4812,19 @@
         <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>300</v>
-      </c>
-      <c r="W59" s="3">
-        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>200</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4697,16 +4833,19 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>200</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
       <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4717,37 +4856,37 @@
         <v>1500</v>
       </c>
       <c r="F60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
-        <v>100</v>
-      </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>200</v>
       </c>
       <c r="Q60" s="3">
         <v>200</v>
@@ -4765,16 +4904,16 @@
         <v>200</v>
       </c>
       <c r="V60" s="3">
+        <v>200</v>
+      </c>
+      <c r="W60" s="3">
         <v>400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>200</v>
       </c>
       <c r="X60" s="3">
         <v>200</v>
       </c>
       <c r="Y60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
@@ -4783,16 +4922,19 @@
         <v>100</v>
       </c>
       <c r="AB60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="3">
         <v>200</v>
       </c>
-      <c r="AC60" s="3">
-        <v>100</v>
-      </c>
       <c r="AD60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4827,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -4877,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4915,8 +5060,8 @@
       <c r="N62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4934,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -4945,8 +5090,8 @@
       <c r="X62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>10</v>
+      <c r="Y62" s="3">
+        <v>100</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>10</v>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,47 +5375,50 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E66" s="3">
         <v>1600</v>
       </c>
       <c r="F66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5271,44 +5428,47 @@
       <c r="R66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S66" s="3">
-        <v>100</v>
+      <c r="S66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U66" s="3">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
-      </c>
-      <c r="W66" s="3">
-        <v>300</v>
       </c>
       <c r="X66" s="3">
         <v>300</v>
       </c>
       <c r="Y66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z66" s="3">
         <v>100</v>
       </c>
       <c r="AA66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB66" s="3">
         <v>200</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>300</v>
       </c>
       <c r="AC66" s="3">
         <v>300</v>
       </c>
       <c r="AD66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-65100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-63500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-57000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-54300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-51600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-49400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-47600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-46900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-45800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-44500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-42200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-40900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-31800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-30700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-28100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-28500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-27800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-23900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-22800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E80" s="2">
         <v>45900</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45808</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45716</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45626</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45535</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45443</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45351</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45260</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45169</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45077</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44985</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44895</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44804</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44712</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44620</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44530</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44439</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44347</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44255</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44165</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44074</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43982</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43890</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43799</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43708</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43616</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-2700</v>
       </c>
       <c r="G81" s="3">
         <v>-2700</v>
       </c>
       <c r="H81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1200</v>
       </c>
       <c r="L81" s="3">
         <v>-1200</v>
       </c>
       <c r="M81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6480,10 +6678,10 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,43 +7137,46 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-1200</v>
       </c>
       <c r="O89" s="3">
         <v>-1200</v>
@@ -6969,13 +7185,13 @@
         <v>-1200</v>
       </c>
       <c r="Q89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="R89" s="3">
         <v>-1300</v>
       </c>
       <c r="S89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="T89" s="3">
         <v>-1200</v>
@@ -6984,34 +7200,37 @@
         <v>-1200</v>
       </c>
       <c r="V89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-600</v>
       </c>
       <c r="Y89" s="3">
         <v>-600</v>
       </c>
       <c r="Z89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-700</v>
       </c>
       <c r="AB89" s="3">
         <v>-700</v>
       </c>
       <c r="AC89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,13 +7261,14 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7062,8 +7282,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>10</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>10</v>
@@ -7071,8 +7291,8 @@
       <c r="K91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7084,22 +7304,22 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>10</v>
@@ -7113,23 +7333,26 @@
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,17 +7526,20 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -7318,23 +7547,23 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -7342,29 +7571,29 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>300</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7381,13 +7610,16 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7689,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,46 +8004,49 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>4300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>5000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -7816,40 +8061,43 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>4000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>9400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
-        <v>100</v>
-      </c>
       <c r="AC100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7865,8 +8113,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>10</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>10</v>
@@ -7895,8 +8143,8 @@
       <c r="Q101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -7934,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-1300</v>
       </c>
       <c r="O102" s="3">
         <v>-1300</v>
       </c>
       <c r="P102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-1300</v>
       </c>
       <c r="R102" s="3">
         <v>-1300</v>
       </c>
       <c r="S102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEXX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>LEXX</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
         <v>45991</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45716</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45626</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45535</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45443</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45351</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45260</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45169</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45077</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44985</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44895</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44804</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44712</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44620</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44530</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44439</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44347</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44255</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44165</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44074</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43982</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43890</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43799</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43708</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43616</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="3">
-        <v>200</v>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
@@ -805,7 +809,7 @@
         <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
@@ -814,19 +818,19 @@
         <v>100</v>
       </c>
       <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
@@ -835,7 +839,7 @@
         <v>100</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -844,66 +848,69 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>200</v>
       </c>
       <c r="X8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>100</v>
       </c>
       <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>10</v>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
+      <c r="L9" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -933,25 +940,25 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3">
         <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="3">
         <v>0</v>
@@ -962,16 +969,19 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3">
-        <v>200</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
@@ -983,7 +993,7 @@
         <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -995,16 +1005,16 @@
         <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
@@ -1013,7 +1023,7 @@
         <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>0</v>
@@ -1022,37 +1032,40 @@
         <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
         <v>200</v>
       </c>
       <c r="Y10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
         <v>100</v>
       </c>
       <c r="AE10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>500</v>
-      </c>
-      <c r="W12" s="3">
-        <v>200</v>
       </c>
       <c r="X12" s="3">
         <v>200</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
-      <c r="AB12" s="3">
-        <v>100</v>
-      </c>
       <c r="AC12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD12" s="3">
         <v>200</v>
       </c>
       <c r="AE12" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,20 +1279,23 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1292,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
@@ -1321,8 +1341,8 @@
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1384,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>10</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>10</v>
@@ -1410,8 +1433,8 @@
       <c r="U15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1426,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,88 +1496,89 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2900</v>
       </c>
       <c r="H17" s="3">
         <v>2900</v>
       </c>
       <c r="I17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>1200</v>
       </c>
       <c r="AD17" s="3">
         <v>1200</v>
@@ -1559,97 +1586,103 @@
       <c r="AE17" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AD18" s="3">
         <v>-1100</v>
       </c>
       <c r="AE18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1722,8 +1756,8 @@
       <c r="O20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1770,97 +1804,103 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-2700</v>
       </c>
       <c r="H21" s="3">
         <v>-2700</v>
       </c>
       <c r="I21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,11 +1925,11 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>10</v>
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>10</v>
@@ -1900,8 +1940,8 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1948,105 +1988,111 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-2700</v>
       </c>
       <c r="H23" s="3">
         <v>-2700</v>
       </c>
       <c r="I23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1200</v>
       </c>
       <c r="M23" s="3">
         <v>-1200</v>
       </c>
       <c r="N23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-1200</v>
       </c>
       <c r="AE23" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>10</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>10</v>
@@ -2078,8 +2124,8 @@
       <c r="O24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-2700</v>
       </c>
       <c r="H26" s="3">
         <v>-2700</v>
       </c>
       <c r="I26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1200</v>
       </c>
       <c r="M26" s="3">
         <v>-1200</v>
       </c>
       <c r="N26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-1200</v>
       </c>
       <c r="AE26" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-2700</v>
       </c>
       <c r="H27" s="3">
         <v>-2700</v>
       </c>
       <c r="I27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-1200</v>
       </c>
       <c r="M27" s="3">
         <v>-1200</v>
       </c>
       <c r="N27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2545,11 +2606,11 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>1500</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -2557,13 +2618,13 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
+      <c r="AC29" s="3">
+        <v>100</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2790,8 +2860,8 @@
       <c r="O32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2838,97 +2908,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-2700</v>
       </c>
       <c r="H33" s="3">
         <v>-2700</v>
       </c>
       <c r="I33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1200</v>
       </c>
       <c r="M33" s="3">
         <v>-1200</v>
       </c>
       <c r="N33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-2700</v>
       </c>
       <c r="H35" s="3">
         <v>-2700</v>
       </c>
       <c r="I35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1200</v>
       </c>
       <c r="M35" s="3">
         <v>-1200</v>
       </c>
       <c r="N35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
         <v>45991</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45716</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45626</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45535</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45443</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45351</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45260</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45169</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45077</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44985</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44895</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44804</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44712</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44620</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44530</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44439</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44347</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44255</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44165</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44074</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43982</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43890</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43799</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43708</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43616</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>1300</v>
       </c>
       <c r="AC41" s="3">
         <v>1300</v>
       </c>
       <c r="AD41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE41" s="3">
         <v>2000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3363,25 +3453,25 @@
         <v>100</v>
       </c>
       <c r="E42" s="3">
+        <v>100</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
@@ -3390,7 +3480,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
@@ -3405,23 +3495,23 @@
         <v>300</v>
       </c>
       <c r="S42" s="3">
+        <v>300</v>
+      </c>
+      <c r="T42" s="3">
         <v>600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>500</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
@@ -3435,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
         <v>100</v>
@@ -3443,97 +3533,103 @@
       <c r="AE42" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>400</v>
       </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
+        <v>200</v>
+      </c>
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
-        <v>100</v>
-      </c>
       <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
-        <v>100</v>
-      </c>
       <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="T43" s="3">
         <v>500</v>
       </c>
       <c r="U43" s="3">
+        <v>500</v>
+      </c>
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>200</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>300</v>
       </c>
       <c r="AC43" s="3">
         <v>300</v>
       </c>
       <c r="AD43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE43" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3570,8 +3666,8 @@
       <c r="N44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3592,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <v>100</v>
@@ -3616,13 +3712,16 @@
         <v>100</v>
       </c>
       <c r="AD44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE44" s="3">
         <v>200</v>
       </c>
-      <c r="AE44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3662,39 +3761,39 @@
       <c r="O45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
-        <v>100</v>
-      </c>
       <c r="AA45" s="3">
         <v>100</v>
       </c>
@@ -3710,97 +3809,103 @@
       <c r="AE45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3849,8 +3954,8 @@
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3858,15 +3963,15 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X47" s="3">
         <v>400</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3882,14 +3987,17 @@
       <c r="AC47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3900,7 +4008,7 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
@@ -3924,13 +4032,13 @@
         <v>400</v>
       </c>
       <c r="N48" s="3">
+        <v>400</v>
+      </c>
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
-      </c>
-      <c r="P48" s="3">
-        <v>400</v>
       </c>
       <c r="Q48" s="3">
         <v>400</v>
@@ -3942,7 +4050,7 @@
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
@@ -3954,19 +4062,19 @@
         <v>500</v>
       </c>
       <c r="X48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y48" s="3">
         <v>600</v>
       </c>
       <c r="Z48" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AA48" s="3">
         <v>500</v>
       </c>
       <c r="AB48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC48" s="3">
         <v>600</v>
@@ -3975,10 +4083,13 @@
         <v>600</v>
       </c>
       <c r="AE48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF48" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3989,7 +4100,7 @@
         <v>300</v>
       </c>
       <c r="F49" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G49" s="3">
         <v>500</v>
@@ -4025,7 +4136,7 @@
         <v>500</v>
       </c>
       <c r="R49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>400</v>
@@ -4040,7 +4151,7 @@
         <v>400</v>
       </c>
       <c r="W49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X49" s="3">
         <v>300</v>
@@ -4061,13 +4172,16 @@
         <v>300</v>
       </c>
       <c r="AD49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4271,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4279,14 +4399,14 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>10</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>2700</v>
       </c>
       <c r="AC54" s="3">
         <v>2700</v>
       </c>
       <c r="AD54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE54" s="3">
         <v>3500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,52 +4707,53 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>600</v>
       </c>
       <c r="F57" s="3">
         <v>600</v>
       </c>
       <c r="G57" s="3">
+        <v>600</v>
+      </c>
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -4631,19 +4762,19 @@
         <v>100</v>
       </c>
       <c r="T57" s="3">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
-        <v>100</v>
-      </c>
       <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
-        <v>100</v>
-      </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -4652,22 +4783,25 @@
         <v>0</v>
       </c>
       <c r="AA57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB57" s="3">
         <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4731,8 +4865,8 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
@@ -4749,14 +4883,17 @@
       <c r="AC58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4775,11 +4912,11 @@
       <c r="H59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>10</v>
+      <c r="I59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>10</v>
@@ -4793,11 +4930,11 @@
       <c r="N59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
@@ -4815,19 +4952,19 @@
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>300</v>
-      </c>
-      <c r="X59" s="3">
-        <v>200</v>
       </c>
       <c r="Y59" s="3">
         <v>200</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4836,21 +4973,24 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
         <v>200</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
       <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>1500</v>
@@ -4859,37 +4999,37 @@
         <v>1500</v>
       </c>
       <c r="G60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
-        <v>100</v>
-      </c>
       <c r="L60" s="3">
         <v>100</v>
       </c>
       <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>200</v>
       </c>
       <c r="R60" s="3">
         <v>200</v>
@@ -4907,16 +5047,16 @@
         <v>200</v>
       </c>
       <c r="W60" s="3">
+        <v>200</v>
+      </c>
+      <c r="X60" s="3">
         <v>400</v>
-      </c>
-      <c r="X60" s="3">
-        <v>200</v>
       </c>
       <c r="Y60" s="3">
         <v>200</v>
       </c>
       <c r="Z60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA60" s="3">
         <v>100</v>
@@ -4925,16 +5065,19 @@
         <v>100</v>
       </c>
       <c r="AC60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD60" s="3">
         <v>200</v>
       </c>
-      <c r="AD60" s="3">
-        <v>100</v>
-      </c>
       <c r="AE60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4972,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5063,8 +5209,8 @@
       <c r="O62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5082,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -5093,8 +5239,8 @@
       <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>10</v>
+      <c r="Z62" s="3">
+        <v>100</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>10</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,50 +5533,53 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1600</v>
       </c>
       <c r="F66" s="3">
         <v>1600</v>
       </c>
       <c r="G66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H66" s="3">
         <v>1900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5431,44 +5589,47 @@
       <c r="S66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T66" s="3">
-        <v>100</v>
+      <c r="T66" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V66" s="3">
+        <v>0</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>300</v>
       </c>
       <c r="Y66" s="3">
         <v>300</v>
       </c>
       <c r="Z66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA66" s="3">
         <v>100</v>
       </c>
       <c r="AB66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC66" s="3">
         <v>200</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>300</v>
       </c>
       <c r="AD66" s="3">
         <v>300</v>
       </c>
       <c r="AE66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF66" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-65100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-63500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-57000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-54300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-51600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-49400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-47600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-46900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-45800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-44500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-42200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-37600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-33800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-31800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-30700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-28100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-27800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-25700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-23900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
         <v>45991</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45716</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45626</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45535</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45443</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45351</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45260</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45169</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45077</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44985</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44895</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44804</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44712</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44620</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44530</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44439</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44347</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44255</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44165</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44074</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43982</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43890</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43799</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43708</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43616</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43524</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-2700</v>
       </c>
       <c r="H81" s="3">
         <v>-2700</v>
       </c>
       <c r="I81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1200</v>
       </c>
       <c r="M81" s="3">
         <v>-1200</v>
       </c>
       <c r="N81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6681,10 +6880,10 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,46 +7354,49 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-1200</v>
       </c>
       <c r="P89" s="3">
         <v>-1200</v>
@@ -7188,13 +7405,13 @@
         <v>-1200</v>
       </c>
       <c r="R89" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="S89" s="3">
         <v>-1300</v>
       </c>
       <c r="T89" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="U89" s="3">
         <v>-1200</v>
@@ -7203,34 +7420,37 @@
         <v>-1200</v>
       </c>
       <c r="W89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-600</v>
       </c>
       <c r="Z89" s="3">
         <v>-600</v>
       </c>
       <c r="AA89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-700</v>
       </c>
       <c r="AC89" s="3">
         <v>-700</v>
       </c>
       <c r="AD89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,16 +7482,17 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7285,8 +7506,8 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>10</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>10</v>
@@ -7294,8 +7515,8 @@
       <c r="L91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7307,22 +7528,22 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>10</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>10</v>
@@ -7336,23 +7557,26 @@
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,20 +7756,23 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -7550,23 +7780,23 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7574,29 +7804,29 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>300</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -7613,13 +7843,16 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7692,8 +7926,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,49 +8250,52 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>5000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -8064,45 +8310,48 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>4000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>9400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
-        <v>100</v>
-      </c>
       <c r="AD100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -8116,8 +8365,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>10</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>10</v>
@@ -8146,8 +8395,8 @@
       <c r="R101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-1300</v>
       </c>
       <c r="P102" s="3">
         <v>-1300</v>
       </c>
       <c r="Q102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-1300</v>
       </c>
       <c r="S102" s="3">
         <v>-1300</v>
       </c>
       <c r="T102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
     </row>
